--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44516</v>
+        <v>44600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44516</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44600</v>
+        <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44516</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44516</v>
+        <v>44897</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1023,14 +1023,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44516</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>44516</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44516</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44516</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44600</v>
+        <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1023,14 +1023,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44516</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44897</v>
+        <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,17 +614,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44516</v>
+        <v>44897</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1023,14 +1023,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44897</v>
+        <v>44516</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>44600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt TRELLEBORG.xlsx
+++ b/Översikt TRELLEBORG.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 57811-2022</t>
+          <t>A 25610-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44897</v>
+        <v>45463</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,46 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25610-2024</t>
+          <t>A 57811-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44897</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,17 +719,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,39 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 25610-2024 artfynd.xlsx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/artfynd/A 57811-2022 artfynd.xlsx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 25610-2024 karta.png", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor/A 57811-2022 karta.png", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 25610-2024 georefererad karta.tif", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/kartor_geotiff/A 57811-2022 georefererad karta.tif", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 25610-2024 FSC-klagomål.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomål/A 57811-2022 FSC-klagomål.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 25610-2024 FSC-klagomål mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/klagomålsmail/A 57811-2022 FSC-klagomål mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 25610-2024 tillsynsbegäran.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsyn/A 57811-2022 tillsynsbegäran.docx", "A 57811-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 25610-2024 tillsynsbegäran mail.docx", "A 25610-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1287/tillsynsmail/A 57811-2022 tillsynsbegäran mail.docx", "A 57811-2022")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +811,7 @@
         <v>44516</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44516</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 57810-2022</t>
+          <t>A 65640-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44897</v>
+        <v>44516</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65640-2021</t>
+          <t>A 6314-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1023,14 +1023,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44516</v>
+        <v>44600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6314-2022</t>
+          <t>A 57810-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44600</v>
+        <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>45887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
